--- a/Win/Notifi.xlsx
+++ b/Win/Notifi.xlsx
@@ -5,19 +5,21 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hostp\Documents\work\job\portfolio\Notification\Lin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hostp\Documents\work\job\portfolio\Notification\Win\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C3C5BE-0B7C-48A1-8633-604FE0B09010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA933534-5CF8-4E53-B413-A8595930EB80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{3D69F8E4-DD0A-472C-9B36-E19B6458F0CA}"/>
   </bookViews>
   <sheets>
     <sheet name="SEIBIS" sheetId="1" r:id="rId1"/>
-    <sheet name="chatW" sheetId="2" r:id="rId2"/>
+    <sheet name="NICO" sheetId="3" r:id="rId2"/>
+    <sheet name="chatW" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">chatW!$A$1:$AJ$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">chatW!$A$1:$AJ$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">NICO!$A$1:$AJ$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SEIBIS!$A$1:$AJ$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>SEIBIS情報</t>
     <rPh sb="6" eb="8">
@@ -95,43 +97,121 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ルームID：</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>招待リンク：</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>https://xxxx</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://yyyy</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://zzzz</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>rykosugi@gmail.com</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>p4HOLcPr</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://aaaa</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>bbbbbbbbbbbbbbbbbbbbbbb</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>00000000000000000</t>
+    <t>NICORAS情報</t>
+    <rPh sb="7" eb="9">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザID：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>page_id：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>actionCount：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>login_stage：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>g-recaptcha-response：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>login_btn：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※セッション有効期限切れの場合、再取得</t>
+    <rPh sb="6" eb="8">
+      <t>ユウコウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ギ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>サイシュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SEIBISルームID：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NICOルームID：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://xxxxxxx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://xxxxxx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>xxxxxx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>yyyyyyy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>xxxxx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>?????</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>xxxyyyzzz@gmail.com</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>abcabc</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://xxxxxxxx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://xxxxx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>abcabcabc</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00000000000</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11111111111111</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -181,7 +261,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -211,6 +291,16 @@
         </stop>
         <stop position="1">
           <color rgb="FFFF99FF"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="270">
+        <stop position="0">
+          <color theme="0"/>
+        </stop>
+        <stop position="1">
+          <color theme="7" tint="0.59999389629810485"/>
         </stop>
       </gradientFill>
     </fill>
@@ -380,7 +470,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -448,6 +538,33 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="14" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -969,7 +1086,7 @@
         <v>3</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -1006,7 +1123,7 @@
         <v>4</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -1043,7 +1160,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
@@ -1080,7 +1197,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
@@ -1117,7 +1234,7 @@
         <v>2</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
@@ -1381,9 +1498,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{378B85EA-7797-42FB-A769-CC6DF4208673}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB3FE4A6-18BD-4FF0-B53B-34766361C868}">
   <sheetPr>
-    <tabColor rgb="FFFF99FF"/>
+    <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:AJ45"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -1393,7 +1510,7 @@
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A1" s="23" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -1551,10 +1668,10 @@
     </row>
     <row r="6" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -1588,9 +1705,11 @@
     </row>
     <row r="8" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="19"/>
+        <v>4</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>25</v>
+      </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
@@ -1623,7 +1742,7 @@
     </row>
     <row r="10" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="8"/>
@@ -1658,35 +1777,35 @@
     </row>
     <row r="12" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="8"/>
-      <c r="AA12" s="8"/>
-      <c r="AB12" s="8"/>
-      <c r="AC12" s="8"/>
-      <c r="AD12" s="8"/>
-      <c r="AE12" s="8"/>
-      <c r="AF12" s="9"/>
+        <v>14</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="21"/>
+      <c r="W12" s="21"/>
+      <c r="X12" s="21"/>
+      <c r="Y12" s="21"/>
+      <c r="Z12" s="21"/>
+      <c r="AA12" s="21"/>
+      <c r="AB12" s="21"/>
+      <c r="AC12" s="21"/>
+      <c r="AD12" s="21"/>
+      <c r="AE12" s="21"/>
+      <c r="AF12" s="22"/>
       <c r="AJ12" s="2"/>
     </row>
     <row r="13" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1695,124 +1814,225 @@
     </row>
     <row r="14" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="21"/>
-      <c r="V14" s="21"/>
-      <c r="W14" s="21"/>
-      <c r="X14" s="21"/>
-      <c r="Y14" s="21"/>
-      <c r="Z14" s="21"/>
-      <c r="AA14" s="21"/>
-      <c r="AB14" s="21"/>
-      <c r="AC14" s="21"/>
-      <c r="AD14" s="21"/>
-      <c r="AE14" s="21"/>
-      <c r="AF14" s="22"/>
+        <v>2</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="8"/>
+      <c r="AA14" s="8"/>
+      <c r="AB14" s="8"/>
+      <c r="AC14" s="8"/>
+      <c r="AD14" s="8"/>
+      <c r="AE14" s="8"/>
+      <c r="AF14" s="9"/>
       <c r="AJ14" s="2"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1"/>
+      <c r="M15" t="s">
+        <v>20</v>
+      </c>
       <c r="AJ15" s="2"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.4">
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
-      <c r="V16" s="6"/>
-      <c r="W16" s="6"/>
-      <c r="X16" s="6"/>
-      <c r="Y16" s="6"/>
-      <c r="Z16" s="6"/>
-      <c r="AA16" s="6"/>
-      <c r="AB16" s="6"/>
-      <c r="AC16" s="6"/>
-      <c r="AD16" s="6"/>
-      <c r="AE16" s="6"/>
-      <c r="AF16" s="6"/>
+    <row r="16" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8"/>
+      <c r="AA16" s="8"/>
+      <c r="AB16" s="8"/>
+      <c r="AC16" s="8"/>
+      <c r="AD16" s="8"/>
+      <c r="AE16" s="8"/>
+      <c r="AF16" s="9"/>
       <c r="AJ16" s="2"/>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1"/>
       <c r="AJ17" s="2"/>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.4">
-      <c r="A18" s="1"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="6"/>
-      <c r="AB18" s="6"/>
-      <c r="AC18" s="6"/>
-      <c r="AD18" s="6"/>
-      <c r="AE18" s="6"/>
-      <c r="AF18" s="6"/>
+    <row r="18" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="21"/>
+      <c r="V18" s="21"/>
+      <c r="W18" s="21"/>
+      <c r="X18" s="21"/>
+      <c r="Y18" s="21"/>
+      <c r="Z18" s="21"/>
+      <c r="AA18" s="21"/>
+      <c r="AB18" s="21"/>
+      <c r="AC18" s="21"/>
+      <c r="AD18" s="21"/>
+      <c r="AE18" s="21"/>
+      <c r="AF18" s="22"/>
       <c r="AJ18" s="2"/>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1"/>
       <c r="AJ19" s="2"/>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.4">
-      <c r="A20" s="1"/>
+    <row r="20" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="21"/>
+      <c r="R20" s="21"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="21"/>
+      <c r="U20" s="21"/>
+      <c r="V20" s="21"/>
+      <c r="W20" s="21"/>
+      <c r="X20" s="21"/>
+      <c r="Y20" s="21"/>
+      <c r="Z20" s="21"/>
+      <c r="AA20" s="21"/>
+      <c r="AB20" s="21"/>
+      <c r="AC20" s="21"/>
+      <c r="AD20" s="21"/>
+      <c r="AE20" s="21"/>
+      <c r="AF20" s="22"/>
       <c r="AJ20" s="2"/>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
       <c r="AJ21" s="2"/>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.4">
-      <c r="A22" s="1"/>
+    <row r="22" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="21"/>
+      <c r="R22" s="21"/>
+      <c r="S22" s="21"/>
+      <c r="T22" s="21"/>
+      <c r="U22" s="21"/>
+      <c r="V22" s="21"/>
+      <c r="W22" s="21"/>
+      <c r="X22" s="21"/>
+      <c r="Y22" s="21"/>
+      <c r="Z22" s="21"/>
+      <c r="AA22" s="21"/>
+      <c r="AB22" s="21"/>
+      <c r="AC22" s="21"/>
+      <c r="AD22" s="21"/>
+      <c r="AE22" s="21"/>
+      <c r="AF22" s="22"/>
       <c r="AJ22" s="2"/>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.4">
-      <c r="A23" s="1"/>
+    <row r="23" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="AJ23" s="2"/>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.4">
-      <c r="A24" s="1"/>
+    <row r="24" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="21"/>
+      <c r="R24" s="21"/>
+      <c r="S24" s="21"/>
+      <c r="T24" s="21"/>
+      <c r="U24" s="21"/>
+      <c r="V24" s="21"/>
+      <c r="W24" s="21"/>
+      <c r="X24" s="21"/>
+      <c r="Y24" s="21"/>
+      <c r="Z24" s="21"/>
+      <c r="AA24" s="21"/>
+      <c r="AB24" s="21"/>
+      <c r="AC24" s="21"/>
+      <c r="AD24" s="21"/>
+      <c r="AE24" s="21"/>
+      <c r="AF24" s="22"/>
       <c r="AJ24" s="2"/>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.4">
@@ -1934,7 +2154,593 @@
       <c r="AJ45" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="11">
+    <mergeCell ref="H14:AF14"/>
+    <mergeCell ref="A1:AJ4"/>
+    <mergeCell ref="H6:AF6"/>
+    <mergeCell ref="H8:AF8"/>
+    <mergeCell ref="H10:AF10"/>
+    <mergeCell ref="H12:AF12"/>
+    <mergeCell ref="H16:AF16"/>
+    <mergeCell ref="H18:AF18"/>
+    <mergeCell ref="H22:AF22"/>
+    <mergeCell ref="H20:AF20"/>
+    <mergeCell ref="H24:AF24"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="H6" r:id="rId1" xr:uid="{58B209D6-65EC-4C7B-9D55-889A9D4EC6BB}"/>
+    <hyperlink ref="H12" r:id="rId2" display="narahara.com@gmail.com" xr:uid="{617376FE-2950-4ED5-9C84-1AD120EC3B04}"/>
+    <hyperlink ref="H8" r:id="rId3" xr:uid="{27DB3AF9-F4D4-4084-83F4-C09933A8CFAD}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="69" orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{378B85EA-7797-42FB-A769-CC6DF4208673}">
+  <sheetPr>
+    <tabColor rgb="FFFF99FF"/>
+  </sheetPr>
+  <dimension ref="A1:AJ45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="702" width="3.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A1" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="33"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="33"/>
+      <c r="AF1" s="33"/>
+      <c r="AG1" s="33"/>
+      <c r="AH1" s="33"/>
+      <c r="AI1" s="33"/>
+      <c r="AJ1" s="34"/>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="36"/>
+      <c r="AE2" s="36"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
+      <c r="AJ2" s="37"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A3" s="35"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="36"/>
+      <c r="Y3" s="36"/>
+      <c r="Z3" s="36"/>
+      <c r="AA3" s="36"/>
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="36"/>
+      <c r="AD3" s="36"/>
+      <c r="AE3" s="36"/>
+      <c r="AF3" s="36"/>
+      <c r="AG3" s="36"/>
+      <c r="AH3" s="36"/>
+      <c r="AI3" s="36"/>
+      <c r="AJ3" s="37"/>
+    </row>
+    <row r="4" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="38"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="39"/>
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39"/>
+      <c r="W4" s="39"/>
+      <c r="X4" s="39"/>
+      <c r="Y4" s="39"/>
+      <c r="Z4" s="39"/>
+      <c r="AA4" s="39"/>
+      <c r="AB4" s="39"/>
+      <c r="AC4" s="39"/>
+      <c r="AD4" s="39"/>
+      <c r="AE4" s="39"/>
+      <c r="AF4" s="39"/>
+      <c r="AG4" s="39"/>
+      <c r="AH4" s="39"/>
+      <c r="AI4" s="39"/>
+      <c r="AJ4" s="40"/>
+    </row>
+    <row r="5" spans="1:36" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="1"/>
+      <c r="AJ5" s="2"/>
+    </row>
+    <row r="6" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="8"/>
+      <c r="AA6" s="8"/>
+      <c r="AB6" s="8"/>
+      <c r="AC6" s="8"/>
+      <c r="AD6" s="8"/>
+      <c r="AE6" s="8"/>
+      <c r="AF6" s="9"/>
+      <c r="AJ6" s="2"/>
+    </row>
+    <row r="7" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="1"/>
+      <c r="AJ7" s="2"/>
+    </row>
+    <row r="8" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="19"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+      <c r="AA8" s="8"/>
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="8"/>
+      <c r="AD8" s="8"/>
+      <c r="AE8" s="8"/>
+      <c r="AF8" s="9"/>
+      <c r="AJ8" s="2"/>
+    </row>
+    <row r="9" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="1"/>
+      <c r="AJ9" s="2"/>
+    </row>
+    <row r="10" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+      <c r="AA10" s="8"/>
+      <c r="AB10" s="8"/>
+      <c r="AC10" s="8"/>
+      <c r="AD10" s="8"/>
+      <c r="AE10" s="8"/>
+      <c r="AF10" s="9"/>
+      <c r="AJ10" s="2"/>
+    </row>
+    <row r="11" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="1"/>
+      <c r="AJ11" s="2"/>
+    </row>
+    <row r="12" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8"/>
+      <c r="AA12" s="8"/>
+      <c r="AB12" s="8"/>
+      <c r="AC12" s="8"/>
+      <c r="AD12" s="8"/>
+      <c r="AE12" s="8"/>
+      <c r="AF12" s="9"/>
+      <c r="AJ12" s="2"/>
+    </row>
+    <row r="13" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="1"/>
+      <c r="AJ13" s="2"/>
+    </row>
+    <row r="14" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="21"/>
+      <c r="AD14" s="21"/>
+      <c r="AE14" s="21"/>
+      <c r="AF14" s="22"/>
+      <c r="AJ14" s="2"/>
+    </row>
+    <row r="15" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="1"/>
+      <c r="AJ15" s="2"/>
+    </row>
+    <row r="16" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
+      <c r="V16" s="21"/>
+      <c r="W16" s="21"/>
+      <c r="X16" s="21"/>
+      <c r="Y16" s="21"/>
+      <c r="Z16" s="21"/>
+      <c r="AA16" s="21"/>
+      <c r="AB16" s="21"/>
+      <c r="AC16" s="21"/>
+      <c r="AD16" s="21"/>
+      <c r="AE16" s="21"/>
+      <c r="AF16" s="22"/>
+      <c r="AJ16" s="2"/>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A17" s="1"/>
+      <c r="AJ17" s="2"/>
+    </row>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A18" s="1"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="6"/>
+      <c r="AC18" s="6"/>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="6"/>
+      <c r="AF18" s="6"/>
+      <c r="AJ18" s="2"/>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A19" s="1"/>
+      <c r="AJ19" s="2"/>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A20" s="1"/>
+      <c r="AJ20" s="2"/>
+    </row>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A21" s="1"/>
+      <c r="AJ21" s="2"/>
+    </row>
+    <row r="22" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A22" s="1"/>
+      <c r="AJ22" s="2"/>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A23" s="1"/>
+      <c r="AJ23" s="2"/>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A24" s="1"/>
+      <c r="AJ24" s="2"/>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A25" s="1"/>
+      <c r="AJ25" s="2"/>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A26" s="1"/>
+      <c r="AJ26" s="2"/>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A27" s="1"/>
+      <c r="AJ27" s="2"/>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A28" s="1"/>
+      <c r="AJ28" s="2"/>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A29" s="1"/>
+      <c r="AJ29" s="2"/>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A30" s="1"/>
+      <c r="AJ30" s="2"/>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A31" s="1"/>
+      <c r="AJ31" s="2"/>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A32" s="1"/>
+      <c r="AJ32" s="2"/>
+    </row>
+    <row r="33" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A33" s="1"/>
+      <c r="AJ33" s="2"/>
+    </row>
+    <row r="34" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A34" s="1"/>
+      <c r="AJ34" s="2"/>
+    </row>
+    <row r="35" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A35" s="1"/>
+      <c r="AJ35" s="2"/>
+    </row>
+    <row r="36" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A36" s="1"/>
+      <c r="AJ36" s="2"/>
+    </row>
+    <row r="37" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A37" s="1"/>
+      <c r="AJ37" s="2"/>
+    </row>
+    <row r="38" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A38" s="1"/>
+      <c r="AJ38" s="2"/>
+    </row>
+    <row r="39" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A39" s="1"/>
+      <c r="AJ39" s="2"/>
+    </row>
+    <row r="40" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A40" s="1"/>
+      <c r="AJ40" s="2"/>
+    </row>
+    <row r="41" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A41" s="1"/>
+      <c r="AJ41" s="2"/>
+    </row>
+    <row r="42" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A42" s="1"/>
+      <c r="AJ42" s="2"/>
+    </row>
+    <row r="43" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A43" s="1"/>
+      <c r="AJ43" s="2"/>
+    </row>
+    <row r="44" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A44" s="1"/>
+      <c r="AJ44" s="2"/>
+    </row>
+    <row r="45" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="3"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="4"/>
+      <c r="T45" s="4"/>
+      <c r="U45" s="4"/>
+      <c r="V45" s="4"/>
+      <c r="W45" s="4"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="4"/>
+      <c r="AA45" s="4"/>
+      <c r="AB45" s="4"/>
+      <c r="AC45" s="4"/>
+      <c r="AD45" s="4"/>
+      <c r="AE45" s="4"/>
+      <c r="AF45" s="4"/>
+      <c r="AG45" s="4"/>
+      <c r="AH45" s="4"/>
+      <c r="AI45" s="4"/>
+      <c r="AJ45" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="H16:AF16"/>
     <mergeCell ref="H14:AF14"/>
     <mergeCell ref="A1:AJ4"/>
     <mergeCell ref="H6:AF6"/>
@@ -1945,8 +2751,9 @@
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="H6" r:id="rId1" xr:uid="{4C46DCAB-17FA-41B7-A889-E52F9D425A8B}"/>
+    <hyperlink ref="H10" r:id="rId2" xr:uid="{F3047ABF-8571-446F-8DCF-CFC9A71CD9CA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="69" orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId2"/>
+  <pageSetup scale="69" orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId3"/>
 </worksheet>
 </file>